--- a/optimized_version/metadata/optimized_vs_original_summary.xlsx
+++ b/optimized_version/metadata/optimized_vs_original_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,100 +439,120 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>selected_centers</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>selected_learning_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>best_shrinkage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>bias_correction_mw</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bin_calibration_enabled</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>ramp_limit_mw</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>val_operational_mape</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>val_mae</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>val_rmse</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>val_r2</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>test_operational_mape</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>test_mae</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>test_rmse</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>test_r2</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>meets_thresholds</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>original_val_mape</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>original_val_mae</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>original_val_rmse</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>original_val_r2</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>original_test_mape</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>original_test_mae</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>original_test_rmse</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>original_test_r2</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>original_summary_available</t>
         </is>
@@ -554,58 +574,50 @@
         <v>80</v>
       </c>
       <c r="E2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.09954532859921272</v>
+      </c>
+      <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
         <v>5.653995999999992</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.604974255150374</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.790194379484523</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.774318596450072</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.928106695549583</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.766988322764913</v>
+        <v>3.313742647047742</v>
       </c>
       <c r="L2" t="n">
-        <v>1.979304578255757</v>
+        <v>1.642430078380745</v>
       </c>
       <c r="M2" t="n">
-        <v>3.558009673155107</v>
+        <v>2.696304835808605</v>
       </c>
       <c r="N2" t="n">
-        <v>0.891820247943255</v>
-      </c>
-      <c r="O2" t="b">
+        <v>0.9320931225393874</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.434813729089702</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.815631520977621</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.444461454807377</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.8986148399498388</v>
+      </c>
+      <c r="S2" t="b">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>not_available</t>
@@ -626,7 +638,27 @@
           <t>not_available</t>
         </is>
       </c>
-      <c r="X2" t="b">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AB2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -643,61 +675,53 @@
         <v>12959</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.002593061898679139</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8.683362000000004</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.080237395346142</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.9836404672006918</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.296788175301708</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8217338979169557</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.372393407091134</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.163875279788921</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.810318338268851</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.9120531387830006</v>
+      </c>
+      <c r="S3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
-        <v>8.683362000000004</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.080359623730277</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.9837936944443549</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.296782826629536</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8217343417304773</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.372438348377197</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.163939188499166</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4.810345662790334</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.9120521396338571</v>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>not_available</t>
@@ -718,7 +742,27 @@
           <t>not_available</t>
         </is>
       </c>
-      <c r="X3" t="b">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AB3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -738,58 +782,50 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.001711417304903762</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>7.172374999999972</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.8267520531078617</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7165347083643779</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.362171291300452</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.95281150703795</v>
-      </c>
       <c r="K4" t="n">
-        <v>0.6107285081631268</v>
+        <v>0.826760962489566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6975179603950928</v>
+        <v>0.7165159424460079</v>
       </c>
       <c r="M4" t="n">
-        <v>3.077455775461146</v>
+        <v>3.36216239327635</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9453150036605613</v>
-      </c>
-      <c r="O4" t="b">
+        <v>0.9528117568073732</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6106872917110348</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.6974508930467787</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.077447039607641</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.9453153141244469</v>
+      </c>
+      <c r="S4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>not_available</t>
@@ -810,7 +846,27 @@
           <t>not_available</t>
         </is>
       </c>
-      <c r="X4" t="b">
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AB4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -830,58 +886,50 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.75</v>
+        <v>180</v>
       </c>
       <c r="F5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.01291066973358213</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
         <v>5.317387999999993</v>
       </c>
-      <c r="G5" t="n">
-        <v>4.390397932478432</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.588276032978833</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.346916927468652</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8941673527175944</v>
-      </c>
       <c r="K5" t="n">
-        <v>4.055214927582856</v>
+        <v>4.140856265711159</v>
       </c>
       <c r="L5" t="n">
-        <v>1.535037086145704</v>
+        <v>1.488505942119955</v>
       </c>
       <c r="M5" t="n">
-        <v>2.256757944218676</v>
+        <v>2.242774379359897</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8944194863707671</v>
-      </c>
-      <c r="O5" t="b">
+        <v>0.9033514378588641</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.043801373118373</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.545502281855159</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.188589863888851</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.9007015252641053</v>
+      </c>
+      <c r="S5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>not_available</t>
@@ -902,7 +950,27 @@
           <t>not_available</t>
         </is>
       </c>
-      <c r="X5" t="b">
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AB5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -922,58 +990,50 @@
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>180</v>
       </c>
       <c r="F6" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.008739539659202933</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>15.31784999999999</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.412633413866037</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.667351040706921</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7.981141265302722</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8349012201140481</v>
-      </c>
       <c r="K6" t="n">
-        <v>1.404355300987256</v>
+        <v>2.412584472137003</v>
       </c>
       <c r="L6" t="n">
-        <v>1.395573986020531</v>
+        <v>3.66733052040326</v>
       </c>
       <c r="M6" t="n">
-        <v>5.678937930546184</v>
+        <v>7.981140071997947</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9904842964527735</v>
-      </c>
-      <c r="O6" t="b">
+        <v>0.8349012694837162</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.404527208181197</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.395706172320308</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.678938424197674</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9904842947984355</v>
+      </c>
+      <c r="S6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>not_available</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>not_available</t>
@@ -994,7 +1054,27 @@
           <t>not_available</t>
         </is>
       </c>
-      <c r="X6" t="b">
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="AB6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1014,63 +1094,75 @@
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.007715060602686563</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>5.10610399999998</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.829138881154948</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.241735727176205</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.115901503766251</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8231005529812438</v>
-      </c>
       <c r="K7" t="n">
-        <v>4.222006812873919</v>
+        <v>3.829444573472466</v>
       </c>
       <c r="L7" t="n">
-        <v>1.494033246411981</v>
+        <v>1.241678702085746</v>
       </c>
       <c r="M7" t="n">
-        <v>2.257902286220251</v>
+        <v>2.115942286795565</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9043692378737367</v>
-      </c>
-      <c r="O7" t="b">
+        <v>0.8230937336043981</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.221972725718088</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.493854921131536</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.257881106461043</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9043710319522735</v>
+      </c>
+      <c r="S7" t="b">
         <v>1</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
         <v>681168.6789247866</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="U7" t="n">
         <v>1.686309218406677</v>
       </c>
-      <c r="R7" t="n">
+      <c r="V7" t="n">
         <v>2.370084393765196</v>
       </c>
-      <c r="S7" t="n">
+      <c r="W7" t="n">
         <v>-0.2390577793121338</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>19939.21652501478</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
         <v>2.799478054046631</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
         <v>3.582504058218</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AA7" t="n">
         <v>-1.540655136108398</v>
       </c>
-      <c r="X7" t="b">
+      <c r="AB7" t="b">
         <v>1</v>
       </c>
     </row>
